--- a/Document/INVERTER/Inverter.xlsx
+++ b/Document/INVERTER/Inverter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\INVERTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386832D7-6993-47B0-8188-72C9B48B616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570AE0C9-23AB-4D91-BB3C-BA8886B5C1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
-  <si>
-    <t>Q1,Q3 ON给L1充电</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>Q2,Q4ON给L充电</t>
   </si>
@@ -40,6 +37,18 @@
   </si>
   <si>
     <t>Q1,Q3 ON给L充电</t>
+  </si>
+  <si>
+    <t>正半周Q3常导通(60hz 8.333ms),Q1打开其实就相当于一个Buck降压电路</t>
+  </si>
+  <si>
+    <t>正半周Q3常导通(60hz 8.333ms),Q2与Q1是互补Q1关闭之后Q2打开相当于Buck降压电路的整流</t>
+  </si>
+  <si>
+    <t>负半周Q4常导通(60hz 8.333ms),Q2打开其实就相当于一个Buck降压电路</t>
+  </si>
+  <si>
+    <t>负半周Q4常导通(60hz 8.333ms),,Q2与Q1是互补Q2关闭之后Q1打开相当于Buck降压电路的整流</t>
   </si>
 </sst>
 </file>
@@ -1129,9 +1138,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>11207</xdr:colOff>
+      <xdr:colOff>17859</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>46716</xdr:rowOff>
+      <xdr:rowOff>77391</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1146,8 +1155,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="7866529" y="7182971"/>
-          <a:ext cx="11207" cy="1055245"/>
+          <a:off x="7893844" y="7182971"/>
+          <a:ext cx="17859" cy="1085920"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1648,6 +1657,50 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>8164</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>185057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>92867</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>48986</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93B4A850-3F41-F92F-1C28-CFBECF8D570F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9152164" y="10091057"/>
+          <a:ext cx="8009503" cy="5197929"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1921,54 +1974,66 @@
   <sheetData>
     <row r="2" spans="3:16" x14ac:dyDescent="0.25">
       <c r="P2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="3:16" x14ac:dyDescent="0.25">
       <c r="P29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Document/INVERTER/Inverter.xlsx
+++ b/Document/INVERTER/Inverter.xlsx
@@ -1,24 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\INVERTER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerStudy\PowerToplogyStudy\Document\INVERTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570AE0C9-23AB-4D91-BB3C-BA8886B5C1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -27,16 +34,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
-    <t>Q2,Q4ON给L充电</t>
+    <t>Q2,Q3续流</t>
   </si>
   <si>
-    <t>Q2,Q3续流</t>
+    <t>Q1,Q3 ON给L充电</t>
   </si>
   <si>
     <t>Q1,Q4续流</t>
   </si>
   <si>
-    <t>Q1,Q3 ON给L充电</t>
+    <t>Q2,Q4ON给L充电</t>
   </si>
   <si>
     <t>正半周Q3常导通(60hz 8.333ms),Q1打开其实就相当于一个Buck降压电路</t>
@@ -54,25 +61,368 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -80,31 +430,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -120,27 +756,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECB89E56-E8A2-7B51-AD36-36A61AD4FD75}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638175" y="571500"/>
-          <a:ext cx="7763958" cy="4029637"/>
+          <a:off x="645795" y="525780"/>
+          <a:ext cx="7854950" cy="3709035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -162,21 +792,15 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>167878</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{715B5A84-77FE-4AFB-6581-7ABC58BA958C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1354932" y="916781"/>
-          <a:ext cx="1496615" cy="13097"/>
+          <a:off x="1374775" y="855345"/>
+          <a:ext cx="1516380" cy="13335"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -215,21 +839,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57042370-F2E7-4144-A8BA-37484CF51A5A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2827734" y="2059781"/>
-          <a:ext cx="5351860" cy="16669"/>
+          <a:off x="2867660" y="1906905"/>
+          <a:ext cx="5441950" cy="17145"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -268,21 +886,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59D18468-43A1-8637-1CF6-B5F2E2CE6B7A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="8170069" y="2065734"/>
-          <a:ext cx="9525" cy="1506141"/>
+          <a:off x="8300085" y="1913255"/>
+          <a:ext cx="9525" cy="1384300"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -321,21 +933,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>172641</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C304914D-D4B4-DDCD-B780-C54AECE233F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2821781" y="934641"/>
-          <a:ext cx="5953" cy="1143000"/>
+          <a:off x="2861310" y="873125"/>
+          <a:ext cx="6350" cy="1051560"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -374,21 +980,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1D2A979-DFE4-63C9-7D0F-83632CFB2616}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="4607719" y="3518297"/>
-          <a:ext cx="3565922" cy="5953"/>
+          <a:off x="4677410" y="3243580"/>
+          <a:ext cx="3625850" cy="6350"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -427,21 +1027,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>41672</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="Straight Arrow Connector 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D63EA94-362A-4B78-80C8-555E7EB93E24}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Arrow Connector 21"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4648200" y="3530203"/>
-          <a:ext cx="7144" cy="892969"/>
+          <a:off x="4718050" y="3255645"/>
+          <a:ext cx="6985" cy="816610"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -482,27 +1076,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29695C36-09A6-4866-8FB6-04B772167FD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="26" name="Picture 25"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8683072" y="473351"/>
-          <a:ext cx="7760646" cy="4029637"/>
+          <a:off x="8789670" y="442595"/>
+          <a:ext cx="7851775" cy="3709670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -524,21 +1112,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="28" name="Straight Arrow Connector 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F16C344B-6E19-D5BB-CDC1-EB676E4C48BB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="Straight Arrow Connector 27"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="10820400" y="1924050"/>
-          <a:ext cx="5276850" cy="9525"/>
+          <a:off x="10949940" y="1771650"/>
+          <a:ext cx="5345430" cy="9525"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -577,21 +1159,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Straight Arrow Connector 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D1353FA-5BB0-6BC3-BEB4-DF60AD4B9EE3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Straight Arrow Connector 30"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16078200" y="1924050"/>
-          <a:ext cx="0" cy="1543050"/>
+          <a:off x="16276320" y="1771650"/>
+          <a:ext cx="0" cy="1421130"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -630,21 +1206,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="Straight Arrow Connector 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2B74517-8E98-D893-A731-88E4D50BD485}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="Straight Arrow Connector 32"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="13154025" y="3419475"/>
-          <a:ext cx="2933700" cy="0"/>
+          <a:off x="13314045" y="3154680"/>
+          <a:ext cx="2971800" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -683,21 +1253,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="Straight Arrow Connector 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A18B74E-CB52-47F3-A195-6255BE40CA4A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Straight Arrow Connector 33"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13178872" y="3426101"/>
-          <a:ext cx="3728" cy="1107799"/>
+          <a:off x="13338810" y="3154680"/>
+          <a:ext cx="3810" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -736,21 +1300,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="Straight Arrow Connector 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB1CFD8D-ACF6-A680-66B6-D7102BE328C5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="Straight Arrow Connector 36"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="10772775" y="4505325"/>
-          <a:ext cx="2419350" cy="9525"/>
+          <a:off x="10902315" y="4154805"/>
+          <a:ext cx="2449830" cy="9525"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -789,21 +1347,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Straight Arrow Connector 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{938F5877-8B29-4E26-A64C-2D8FED6DD61F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="Straight Arrow Connector 37"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="10815801" y="1905000"/>
-          <a:ext cx="9854" cy="2628900"/>
+          <a:off x="10922635" y="1752600"/>
+          <a:ext cx="10160" cy="2430780"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -844,27 +1396,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7F12D60-5909-46D8-B68E-64631C2D81CF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="45" name="Picture 44"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="571500" y="5748618"/>
-          <a:ext cx="7710169" cy="4029637"/>
+          <a:off x="571500" y="5290820"/>
+          <a:ext cx="7867015" cy="3709670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -888,27 +1434,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{658F3834-C9E3-43AC-B510-A91CEE15DFB5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="46" name="Picture 45"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9230942" y="5535706"/>
-          <a:ext cx="7779723" cy="4029637"/>
+          <a:off x="9324975" y="5093335"/>
+          <a:ext cx="7855585" cy="3709670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -930,21 +1470,15 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>167878</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="Straight Arrow Connector 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A33AF77D-0D7E-4E6B-A51C-9C9C28BFE002}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="Straight Arrow Connector 46"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1354932" y="916781"/>
-          <a:ext cx="1492414" cy="13097"/>
+          <a:off x="1378585" y="855345"/>
+          <a:ext cx="1517015" cy="13335"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -983,21 +1517,15 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>181186</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Straight Arrow Connector 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D47D74EC-5433-4EAD-921D-1E0D74B9290A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="Straight Arrow Connector 47"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2902324" y="6073588"/>
-          <a:ext cx="1580029" cy="13098"/>
+          <a:off x="2950210" y="5600700"/>
+          <a:ext cx="1616710" cy="7620"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1036,21 +1564,15 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="50" name="Straight Arrow Connector 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31D4F8BA-A026-44AB-9882-772C2A3603F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="Straight Arrow Connector 49"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="4426324" y="6062383"/>
-          <a:ext cx="11206" cy="2173941"/>
+          <a:off x="4511040" y="5589905"/>
+          <a:ext cx="10795" cy="1990725"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1089,21 +1611,15 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Straight Arrow Connector 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5330D25-16DC-4DDF-B683-2FBEF3108B8C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="Straight Arrow Connector 51"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4426323" y="8204598"/>
-          <a:ext cx="3485030" cy="42931"/>
+          <a:off x="4510405" y="7548880"/>
+          <a:ext cx="3557905" cy="43180"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1142,21 +1658,15 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>77391</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Straight Arrow Connector 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBA45A8F-0A3E-4B6E-84C7-9D4A83C8296B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Straight Arrow Connector 54"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="7893844" y="7182971"/>
-          <a:ext cx="17859" cy="1085920"/>
+          <a:off x="8023860" y="6618605"/>
+          <a:ext cx="17780" cy="994410"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1195,21 +1705,15 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="58" name="Straight Arrow Connector 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A9F0BC-757C-4FEF-B1D5-671BBDC53BA9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="Straight Arrow Connector 57"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="2891118" y="7240892"/>
-          <a:ext cx="4986617" cy="42932"/>
+          <a:off x="2939415" y="6661150"/>
+          <a:ext cx="5095240" cy="43180"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1248,21 +1752,15 @@
       <xdr:row>50</xdr:row>
       <xdr:rowOff>78441</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="Straight Arrow Connector 60">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94AEC2F2-5F15-4B8C-938A-A8B8D915735D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="Straight Arrow Connector 60"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="2913529" y="7261412"/>
-          <a:ext cx="11206" cy="2342029"/>
+          <a:off x="2961640" y="6682105"/>
+          <a:ext cx="11430" cy="2159000"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1301,21 +1799,15 @@
       <xdr:row>36</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="63" name="Straight Arrow Connector 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2002E86-C6BF-4AB7-9E49-15B0C9E9C73A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="Straight Arrow Connector 62"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14697635" y="6855410"/>
-          <a:ext cx="1931894" cy="13796"/>
+          <a:off x="14987905" y="6309360"/>
+          <a:ext cx="1967865" cy="10795"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1354,21 +1846,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>78828</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="65" name="Straight Arrow Connector 64">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{988FEE99-3B7D-467F-B38E-A2A058C26C0F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="65" name="Straight Arrow Connector 64"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16729996" y="6846795"/>
-          <a:ext cx="14297" cy="1233033"/>
+          <a:off x="16899890" y="6309360"/>
+          <a:ext cx="14605" cy="1130300"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1407,21 +1893,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>59121</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="67" name="Straight Arrow Connector 66">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9B4B511-1048-4257-AFF0-51499DE19B8D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="67" name="Straight Arrow Connector 66"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="13221396" y="8055137"/>
-          <a:ext cx="3522897" cy="4984"/>
+          <a:off x="13353415" y="7414895"/>
+          <a:ext cx="3561080" cy="5080"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1460,21 +1940,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>48261</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="73" name="Straight Arrow Connector 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2DFAA07-5F51-4F22-BCC2-FB5FA4BE8BBD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="Straight Arrow Connector 72"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="13256172" y="5662448"/>
-          <a:ext cx="17776" cy="2386813"/>
+          <a:off x="13388340" y="5220335"/>
+          <a:ext cx="17780" cy="2188845"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1513,21 +1987,15 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>170793</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="76" name="Straight Arrow Connector 75">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A874A29-10A9-4168-8697-DEB3A46A11E3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="76" name="Straight Arrow Connector 75"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11482551" y="5682155"/>
-          <a:ext cx="1786759" cy="13138"/>
+          <a:off x="11595735" y="5240020"/>
+          <a:ext cx="1805940" cy="12700"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1566,21 +2034,15 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>65690</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="79" name="Straight Arrow Connector 78">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17DD0441-749D-4461-988D-1EF9496873D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="79" name="Straight Arrow Connector 78"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11521965" y="5682155"/>
-          <a:ext cx="6569" cy="1432035"/>
+          <a:off x="11635105" y="5240020"/>
+          <a:ext cx="6350" cy="1310005"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1619,21 +2081,15 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>45983</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="81" name="Straight Arrow Connector 80">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9BD9145-DC55-4FE7-9F11-B3083CC0D96B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="Straight Arrow Connector 80"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11521965" y="7094483"/>
-          <a:ext cx="2653863" cy="0"/>
+          <a:off x="11635105" y="6530340"/>
+          <a:ext cx="2685415" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1674,27 +2130,21 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93B4A850-3F41-F92F-1C28-CFBECF8D570F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="13" name="Picture 12"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9152164" y="10091057"/>
-          <a:ext cx="8009503" cy="5197929"/>
+          <a:off x="9265920" y="9288780"/>
+          <a:ext cx="8108950" cy="4780915"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1749,7 +2199,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1784,7 +2234,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1958,74 +2408,69 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="2" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:16">
       <c r="P2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="3:16">
+      <c r="C3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:16">
       <c r="P29" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:16">
       <c r="C30" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5">
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5">
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5">
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5">
       <c r="B57">
         <v>4</v>
       </c>
@@ -2038,6 +2483,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Document/INVERTER/Inverter.xlsx
+++ b/Document/INVERTER/Inverter.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PowerStudy\PowerToplogyStudy\Document\INVERTER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\INVERTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_489B4019F7F13DE4AB2B37673F7C76063BE65733" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,368 +62,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -430,317 +88,31 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -756,13 +128,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -792,9 +170,15 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>167878</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -839,9 +223,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -886,9 +276,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -933,9 +329,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>172641</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="Straight Arrow Connector 16"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -980,9 +382,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="Straight Arrow Connector 19"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1027,9 +435,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>41672</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="Straight Arrow Connector 21"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Straight Arrow Connector 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1076,13 +490,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 25"/>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1112,9 +532,15 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="28" name="Straight Arrow Connector 27"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="Straight Arrow Connector 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1159,9 +585,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="31" name="Straight Arrow Connector 30"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Straight Arrow Connector 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1206,9 +638,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="Straight Arrow Connector 32"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="Straight Arrow Connector 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1253,9 +691,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="Straight Arrow Connector 33"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="34" name="Straight Arrow Connector 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1300,9 +744,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="Straight Arrow Connector 36"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="Straight Arrow Connector 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1347,9 +797,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="38" name="Straight Arrow Connector 37"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="Straight Arrow Connector 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1396,13 +852,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Picture 44"/>
+        <xdr:cNvPr id="45" name="Picture 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1434,13 +896,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Picture 45"/>
+        <xdr:cNvPr id="46" name="Picture 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1470,9 +938,15 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>167878</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="47" name="Straight Arrow Connector 46"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="47" name="Straight Arrow Connector 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1517,9 +991,15 @@
       <xdr:row>31</xdr:row>
       <xdr:rowOff>181186</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="48" name="Straight Arrow Connector 47"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="48" name="Straight Arrow Connector 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1564,9 +1044,15 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="50" name="Straight Arrow Connector 49"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="50" name="Straight Arrow Connector 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1611,9 +1097,15 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>56029</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="Straight Arrow Connector 51"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="Straight Arrow Connector 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1658,9 +1150,15 @@
       <xdr:row>43</xdr:row>
       <xdr:rowOff>77391</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="55" name="Straight Arrow Connector 54"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Straight Arrow Connector 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1705,9 +1203,15 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="58" name="Straight Arrow Connector 57"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="Straight Arrow Connector 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1752,9 +1256,15 @@
       <xdr:row>50</xdr:row>
       <xdr:rowOff>78441</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="61" name="Straight Arrow Connector 60"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="61" name="Straight Arrow Connector 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1799,9 +1309,15 @@
       <xdr:row>36</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="63" name="Straight Arrow Connector 62"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="63" name="Straight Arrow Connector 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1846,9 +1362,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>78828</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="65" name="Straight Arrow Connector 64"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="65" name="Straight Arrow Connector 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1893,9 +1415,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>59121</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="67" name="Straight Arrow Connector 66"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="67" name="Straight Arrow Connector 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1940,9 +1468,15 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>48261</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="73" name="Straight Arrow Connector 72"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="73" name="Straight Arrow Connector 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1987,9 +1521,15 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>170793</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="76" name="Straight Arrow Connector 75"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="76" name="Straight Arrow Connector 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2034,9 +1574,15 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>65690</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="79" name="Straight Arrow Connector 78"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="79" name="Straight Arrow Connector 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2081,9 +1627,15 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>45983</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="81" name="Straight Arrow Connector 80"/>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="Straight Arrow Connector 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2130,13 +1682,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12"/>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2408,14 +1966,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P57"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="3:16">
       <c r="P2" t="s">
@@ -2483,7 +2041,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Document/INVERTER/Inverter.xlsx
+++ b/Document/INVERTER/Inverter.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\INVERTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_489B4019F7F13DE4AB2B37673F7C76063BE65733" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE9852B-776B-4B3D-B589-41CBEFA14B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="matlab reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Q2,Q3续流</t>
   </si>
@@ -58,15 +59,29 @@
   <si>
     <t>负半周Q4常导通(60hz 8.333ms),,Q2与Q1是互补Q2关闭之后Q1打开相当于Buck降压电路的整流</t>
   </si>
+  <si>
+    <t>(10 条消息) 手把手搭建Simulink电力电子控制仿真——（2）H桥逆变器&amp;无差拍预测电流控制 - 知乎</t>
+  </si>
+  <si>
+    <t>https://ww2.mathworks.cn/matlabcentral/fileexchange/182269-closed-loop-single-phase-inverter?s_tid=FX_rc2_behav</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -89,13 +104,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2043,4 +2061,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C43FACF5-A33A-4717-BEF0-92A7E79FF86A}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" display="https://zhuanlan.zhihu.com/p/1974167027729051931" xr:uid="{9E44B704-38E2-4707-9AD2-E4167D849694}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>